--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -531,10 +531,10 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G2">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="H2">
         <v>33</v>
@@ -575,10 +575,10 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="G3">
-        <v>6.55</v>
+        <v>7.55</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -707,10 +707,10 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G6">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -751,10 +751,10 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G15">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="H15">
         <v>6</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -55,7 +55,7 @@
     <t>% Yellow ODP</t>
   </si>
   <si>
-    <t>Total PS</t>
+    <t>PS Diakui</t>
   </si>
   <si>
     <t>REGION</t>
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="F2">
-        <v>135</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>33</v>
@@ -555,7 +555,7 @@
         <v>9.5</v>
       </c>
       <c r="N2">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -569,16 +569,16 @@
         <v>11</v>
       </c>
       <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>27.3</v>
+      </c>
+      <c r="F3">
         <v>11</v>
       </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-      <c r="F3">
-        <v>83</v>
-      </c>
       <c r="G3">
-        <v>7.55</v>
+        <v>3.67</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -599,7 +599,7 @@
         <v>18.2</v>
       </c>
       <c r="N3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -613,16 +613,16 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -643,7 +643,7 @@
         <v>50</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>3.4</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>26</v>
@@ -687,7 +687,7 @@
         <v>3.4</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -701,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>74</v>
-      </c>
       <c r="G6">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -731,7 +731,7 @@
         <v>20</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -751,10 +751,10 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -789,16 +789,16 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -819,7 +819,7 @@
         <v>50</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>3.4</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>26</v>
@@ -863,7 +863,7 @@
         <v>3.4</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -883,10 +883,10 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -921,16 +921,16 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>50</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -965,16 +965,16 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1009,16 +1009,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="F13">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>17</v>
@@ -1039,7 +1039,7 @@
         <v>5.3</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1053,16 +1053,16 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1097,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15">
         <v>10</v>
       </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-      <c r="F15">
-        <v>74</v>
-      </c>
       <c r="G15">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -1127,7 +1127,7 @@
         <v>20</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E2">
-        <v>9.5</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="H2">
         <v>33</v>
@@ -569,16 +569,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>27.3</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="G3">
-        <v>3.67</v>
+        <v>6.55</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -613,16 +613,16 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>3.4</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="H5">
         <v>26</v>
@@ -701,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -751,10 +751,10 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -789,16 +789,16 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>3.4</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="H9">
         <v>26</v>
@@ -883,10 +883,10 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -921,16 +921,16 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -965,16 +965,16 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1009,13 +1009,13 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E13">
-        <v>5.3</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1053,16 +1053,16 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1097,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="H15">
         <v>6</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>45.2</v>
       </c>
       <c r="F2">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>2.93</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>33</v>
@@ -569,16 +569,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -619,10 +619,10 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>58.6</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>26</v>
@@ -701,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -745,16 +745,16 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -795,10 +795,10 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>58.6</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G9">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>26</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -927,10 +927,10 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -965,16 +965,16 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1009,13 +1009,13 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1053,16 +1053,16 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1097,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>6</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>45.2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>33</v>
@@ -613,16 +613,16 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>58.6</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>26</v>
@@ -789,16 +789,16 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>58.6</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>26</v>
@@ -921,16 +921,16 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1009,16 +1009,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>89.5</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>17</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>33</v>
@@ -613,16 +613,16 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>26</v>
@@ -789,16 +789,16 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>26</v>
@@ -921,16 +921,16 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1053,16 +1053,16 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>4</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>9.5</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>33</v>
@@ -569,16 +569,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -657,13 +657,13 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>6.9</v>
+        <v>10.3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -701,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -745,16 +745,16 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -833,13 +833,13 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>6.9</v>
+        <v>10.3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1009,16 +1009,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>17</v>
@@ -1097,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>6</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,28 +525,28 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>73.8</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3.42</v>
       </c>
       <c r="H2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I2">
-        <v>78.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>11.9</v>
+        <v>16.7</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -555,7 +555,7 @@
         <v>9.5</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -569,28 +569,28 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>27.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G3">
-        <v>3.67</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>54.5</v>
+        <v>45.5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>27.3</v>
+        <v>36.4</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -599,7 +599,7 @@
         <v>18.2</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -619,10 +619,10 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -657,28 +657,28 @@
         <v>29</v>
       </c>
       <c r="D5">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>65.5</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>1.26</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>86.2</v>
+      </c>
+      <c r="J5">
         <v>3</v>
       </c>
-      <c r="E5">
+      <c r="K5">
         <v>10.3</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>26</v>
-      </c>
-      <c r="I5">
-        <v>89.7</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>6.9</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>3.4</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -701,28 +701,28 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="G6">
+        <v>6.56</v>
+      </c>
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
       <c r="I6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -731,7 +731,7 @@
         <v>20</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -795,10 +795,10 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -833,28 +833,28 @@
         <v>29</v>
       </c>
       <c r="D9">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>65.5</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>1.26</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>86.2</v>
+      </c>
+      <c r="J9">
         <v>3</v>
       </c>
-      <c r="E9">
+      <c r="K9">
         <v>10.3</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>26</v>
-      </c>
-      <c r="I9">
-        <v>89.7</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9">
-        <v>6.9</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -863,7 +863,7 @@
         <v>3.4</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -927,10 +927,10 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -965,16 +965,16 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1009,13 +1009,13 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>5.3</v>
+        <v>47.4</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1053,28 +1053,28 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1097,28 +1097,28 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="G15">
+        <v>6.56</v>
+      </c>
+      <c r="H15">
         <v>5</v>
       </c>
-      <c r="H15">
-        <v>6</v>
-      </c>
       <c r="I15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L15">
         <v>2</v>
@@ -1127,7 +1127,7 @@
         <v>20</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>73.8</v>
+        <v>83.3</v>
       </c>
       <c r="F2">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G2">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="H2">
         <v>31</v>
@@ -569,16 +569,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>65.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="H5">
         <v>25</v>
@@ -701,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6">
-        <v>6.56</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -751,10 +751,10 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>65.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="H9">
         <v>25</v>
@@ -883,10 +883,10 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -971,10 +971,10 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1009,16 +1009,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>47.4</v>
+        <v>63.2</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="H13">
         <v>17</v>
@@ -1097,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15">
-        <v>6.56</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>5</v>
